--- a/data/gated_research/tennis.xlsx
+++ b/data/gated_research/tennis.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CP$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -979,6 +979,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1447,9 +1448,14 @@
           <t>schedule_missingness</t>
         </is>
       </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
+  <autoFilter ref="A1:CP1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/gated_research/tennis.xlsx
+++ b/data/gated_research/tennis.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CP$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,109 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP5" headerRowCount="1">
+  <autoFilter ref="A1:CP5"/>
+  <tableColumns count="94">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="rest_disparity"/>
+    <tableColumn id="91" name="back_to_back_gap"/>
+    <tableColumn id="92" name="games_last_7_gap"/>
+    <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$5)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$5)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP1"/>
+  <dimension ref="A1:CP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1454,9 +1582,1083 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>3f43a0b023884b3e</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:50:00.179683Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>888-2026:179014</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Alexandra Eala</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.821797</v>
+      </c>
+      <c r="P2" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q2" s="28" t="n">
+        <v>0.231633</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="n"/>
+      <c r="W2" s="26" t="n"/>
+      <c r="X2" s="26" t="n"/>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n"/>
+      <c r="AD2" s="24" t="n"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Alexandra Eala p=0.178 vs Jessica Pegula. Executable ask 0.5900 (aec-wta-jespeg-aleeal-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Alexandra Eala</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Alexandra Eala</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Alexandra Eala</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:52.794231Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>829b8cbbfb0f4113</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:50:00.179683Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>1067-2026:179469</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Darja Vidmanova</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.639939</v>
+      </c>
+      <c r="P3" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q3" s="28" t="n">
+        <v>0.149743</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="n"/>
+      <c r="W3" s="26" t="n"/>
+      <c r="X3" s="26" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n"/>
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Darja Vidmanova p=0.640 vs Kristina Liutova. Executable ask 0.4900 (aec-wta-kriliu-darvid-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>Darja Vidmanova</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>Darja Vidmanova</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>Darja Vidmanova</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>Kristina Liutova</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:42.019193Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>3bcf2798d4e240e4</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:50:00.179683Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182241</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Anna Blinkova</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Rebecca Sramkova</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.53051</v>
+      </c>
+      <c r="P4" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q4" s="28" t="n">
+        <v>0.06968100000000001</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="n"/>
+      <c r="W4" s="26" t="n"/>
+      <c r="X4" s="26" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n"/>
+      <c r="AD4" s="24" t="n"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Anna Blinkova p=0.469 vs Rebecca Sramkova. Executable ask 0.4600 (aec-wta-rebsra-annbli-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>Anna Blinkova</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>Anna Blinkova</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>Anna Blinkova</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>Rebecca Sramkova</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>Rebecca Sramkova</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>Rebecca Sramkova</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:49.636292Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n"/>
+      <c r="BK4" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN4" s="28" t="n"/>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="n"/>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
+      <c r="CB4" s="24" t="n"/>
+      <c r="CC4" s="24" t="n"/>
+      <c r="CD4" s="24" t="n"/>
+      <c r="CE4" s="24" t="n"/>
+      <c r="CF4" s="24" t="n"/>
+      <c r="CG4" s="24" t="n"/>
+      <c r="CH4" s="24" t="n"/>
+      <c r="CI4" s="24" t="n"/>
+      <c r="CJ4" s="24" t="n"/>
+      <c r="CK4" s="24" t="n"/>
+      <c r="CL4" s="24" t="n"/>
+      <c r="CM4" s="24" t="n"/>
+      <c r="CN4" s="24" t="n"/>
+      <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>3c0125b28d7640ca</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:50:00.179683Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Lanlana Tararudee</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Emerson Jones</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.756798</v>
+      </c>
+      <c r="P5" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q5" s="28" t="n">
+        <v>0.106448</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="n"/>
+      <c r="W5" s="26" t="n"/>
+      <c r="X5" s="26" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n"/>
+      <c r="AD5" s="24" t="n"/>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6500 (aec-wta-emejon-lantar-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>Lanlana Tararudee</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Lanlana Tararudee</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Lanlana Tararudee</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>Emerson Jones</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>Emerson Jones</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>Emerson Jones</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:51.741348Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CP1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/gated_research/tennis.xlsx
+++ b/data/gated_research/tennis.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP5" headerRowCount="1">
-  <autoFilter ref="A1:CP5"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ4" headerRowCount="1">
+  <autoFilter ref="A1:CQ4"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -753,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$5)</f>
+        <f>COUNTA('Picks'!$A$2:$A$4)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$4,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")+COUNTIFS('Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$4,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")/(COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")+COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$4)/SUM('Picks'!$BX$2:$BX$4),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$5)</f>
+        <f>SUM('Picks'!$BY$2:$BY$4)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$4,"&lt;&gt;",'Picks'!$AB$2:$AB$4),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$4,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$4,'Picks'!$AM$2:$AM$4,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP5"/>
+  <dimension ref="A1:CQ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1844,7 +1851,8 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
-      <c r="CP2" s="24" t="inlineStr">
+      <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1853,12 +1861,12 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>829b8cbbfb0f4113</t>
+          <t>b67cbdffd65145f7</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
@@ -2066,7 +2074,7 @@
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:42.019193Z</t>
+          <t>2026-08-02T16:10:21.022990Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2112,7 +2120,8 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
-      <c r="CP3" s="24" t="inlineStr">
+      <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2121,22 +2130,22 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>3bcf2798d4e240e4</t>
+          <t>27593d79e6f1489d</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
+          <t>2026-08-02T16:13:39.503934Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:30Z</t>
+          <t>2026-08-02T20:00Z</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182241</t>
+          <t>421-2026:182273</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2146,12 +2155,12 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -2161,7 +2170,7 @@
       </c>
       <c r="I4" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J4" s="25" t="n"/>
@@ -2171,28 +2180,28 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>117</v>
+        <v>-186</v>
       </c>
       <c r="M4" s="27" t="n">
-        <v>2.17</v>
+        <v>1.537634</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.65035</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.53051</v>
+        <v>0.756798</v>
       </c>
       <c r="P4" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>0.06968100000000001</v>
+        <v>0.106448</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="S4" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
@@ -2215,7 +2224,7 @@
       <c r="AD4" s="24" t="n"/>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Anna Blinkova p=0.469 vs Rebecca Sramkova. Executable ask 0.4600 (aec-wta-rebsra-annbli-2026-08-02).</t>
+          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6500 (aec-wta-emejon-lantar-2026-08-02).</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2256,32 +2265,32 @@
       </c>
       <c r="AP4" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AQ4" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AR4" s="24" t="inlineStr">
         <is>
-          <t>Anna Blinkova</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AS4" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AT4" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AU4" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>Emerson Jones</t>
         </is>
       </c>
       <c r="AV4" s="24" t="n"/>
@@ -2334,7 +2343,7 @@
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:46:49.636292Z</t>
+          <t>2026-08-02T16:10:31.074598Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2344,13 +2353,13 @@
       </c>
       <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
-        <v>117</v>
+        <v>-186</v>
       </c>
       <c r="BL4" s="27" t="n">
-        <v>2.17</v>
+        <v>1.537634</v>
       </c>
       <c r="BM4" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.65035</v>
       </c>
       <c r="BN4" s="28" t="n"/>
       <c r="BO4" s="28" t="n"/>
@@ -2380,275 +2389,8 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
-      <c r="CP4" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t>3c0125b28d7640ca</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T15:50:00.179683Z</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T20:00Z</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>421-2026:182273</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
-        <is>
-          <t>TENNIS</t>
-        </is>
-      </c>
-      <c r="F5" s="24" t="inlineStr">
-        <is>
-          <t>Lanlana Tararudee</t>
-        </is>
-      </c>
-      <c r="G5" s="24" t="inlineStr">
-        <is>
-          <t>Emerson Jones</t>
-        </is>
-      </c>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I5" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L5" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="M5" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="N5" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="O5" s="28" t="n">
-        <v>0.756798</v>
-      </c>
-      <c r="P5" s="28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q5" s="28" t="n">
-        <v>0.106448</v>
-      </c>
-      <c r="R5" s="26" t="n">
-        <v>73</v>
-      </c>
-      <c r="S5" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="U5" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
-      <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="26" t="n"/>
-      <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
-      <c r="AE5" s="31" t="inlineStr">
-        <is>
-          <t>Surface-blended Elo on Hard: Lanlana Tararudee p=0.757 vs Emerson Jones. Executable ask 0.6500 (aec-wta-emejon-lantar-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF5" s="31" t="inlineStr">
-        <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
-        </is>
-      </c>
-      <c r="AG5" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH5" s="24" t="n"/>
-      <c r="AI5" s="31" t="n"/>
-      <c r="AJ5" s="31" t="n"/>
-      <c r="AK5" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL5" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM5" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN5" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO5" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP5" s="24" t="inlineStr">
-        <is>
-          <t>Lanlana Tararudee</t>
-        </is>
-      </c>
-      <c r="AQ5" s="24" t="inlineStr">
-        <is>
-          <t>Lanlana Tararudee</t>
-        </is>
-      </c>
-      <c r="AR5" s="24" t="inlineStr">
-        <is>
-          <t>Lanlana Tararudee</t>
-        </is>
-      </c>
-      <c r="AS5" s="24" t="inlineStr">
-        <is>
-          <t>Emerson Jones</t>
-        </is>
-      </c>
-      <c r="AT5" s="24" t="inlineStr">
-        <is>
-          <t>Emerson Jones</t>
-        </is>
-      </c>
-      <c r="AU5" s="24" t="inlineStr">
-        <is>
-          <t>Emerson Jones</t>
-        </is>
-      </c>
-      <c r="AV5" s="24" t="n"/>
-      <c r="AW5" s="24" t="n"/>
-      <c r="AX5" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY5" s="24" t="n"/>
-      <c r="AZ5" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA5" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BB5" s="24" t="inlineStr">
-        <is>
-          <t>surface_blended_elo</t>
-        </is>
-      </c>
-      <c r="BC5" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD5" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BE5" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BF5" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG5" s="24" t="inlineStr">
-        <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
-        </is>
-      </c>
-      <c r="BH5" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T15:46:51.741348Z</t>
-        </is>
-      </c>
-      <c r="BI5" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ5" s="25" t="n"/>
-      <c r="BK5" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="BL5" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="BM5" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="BN5" s="28" t="n"/>
-      <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
-      <c r="BR5" s="28" t="n"/>
-      <c r="BS5" s="28" t="n"/>
-      <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
-      <c r="BV5" s="29" t="n"/>
-      <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n"/>
-      <c r="BY5" s="27" t="n"/>
-      <c r="BZ5" s="24" t="n"/>
-      <c r="CA5" s="31" t="n"/>
-      <c r="CB5" s="24" t="n"/>
-      <c r="CC5" s="24" t="n"/>
-      <c r="CD5" s="24" t="n"/>
-      <c r="CE5" s="24" t="n"/>
-      <c r="CF5" s="24" t="n"/>
-      <c r="CG5" s="24" t="n"/>
-      <c r="CH5" s="24" t="n"/>
-      <c r="CI5" s="24" t="n"/>
-      <c r="CJ5" s="24" t="n"/>
-      <c r="CK5" s="24" t="n"/>
-      <c r="CL5" s="24" t="n"/>
-      <c r="CM5" s="24" t="n"/>
-      <c r="CN5" s="24" t="n"/>
-      <c r="CO5" s="24" t="n"/>
-      <c r="CP5" s="24" t="inlineStr">
+      <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/tennis.xlsx
+++ b/data/gated_research/tennis.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ4" headerRowCount="1">
-  <autoFilter ref="A1:CQ4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ7" headerRowCount="1">
+  <autoFilter ref="A1:CQ7"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$4)</f>
+        <f>COUNTA('Picks'!$A$2:$A$7)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$4,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")+COUNTIFS('Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$4,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")/(COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")+COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$4)/SUM('Picks'!$BX$2:$BX$4),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$4)</f>
+        <f>SUM('Picks'!$BY$2:$BY$7)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$4,"&lt;&gt;",'Picks'!$AB$2:$AB$4),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$4,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$4,'Picks'!$AM$2:$AM$4,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ4"/>
+  <dimension ref="A1:CQ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1861,12 +1861,12 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>b67cbdffd65145f7</t>
+          <t>124dce8010354e36</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AF3" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG3" s="24" t="inlineStr">
@@ -2034,12 +2034,12 @@
       <c r="AY3" s="24" t="n"/>
       <c r="AZ3" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BG3" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:21.022990Z</t>
+          <t>2026-08-02T16:47:46.960029Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2130,12 +2130,12 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>27593d79e6f1489d</t>
+          <t>6d7f432ea3404e13</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:39.503934Z</t>
+          <t>2026-08-02T16:51:36.214335Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AF4" s="31" t="inlineStr">
         <is>
-          <t>Research-only surface-blended Elo model; singles only, WTA-only market coverage, not yet locked-holdout qualified.</t>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
         </is>
       </c>
       <c r="AG4" s="24" t="inlineStr">
@@ -2303,12 +2303,12 @@
       <c r="AY4" s="24" t="n"/>
       <c r="AZ4" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="BG4" s="24" t="inlineStr">
         <is>
-          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
         </is>
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:31.074598Z</t>
+          <t>2026-08-02T16:47:57.265599Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2396,6 +2396,813 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>bc41de4f0d1a4289</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181785</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Titouan Droguet</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Luca Van Assche</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.561017</v>
+      </c>
+      <c r="P5" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q5" s="28" t="n">
+        <v>0.070821</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="n"/>
+      <c r="W5" s="26" t="n"/>
+      <c r="X5" s="26" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n"/>
+      <c r="AD5" s="24" t="n"/>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Titouan Droguet p=0.561 vs Luca Van Assche. Executable ask 0.4900 (aec-atp-lucass-titdro-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>Titouan Droguet</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Titouan Droguet</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Titouan Droguet</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>Luca Van Assche</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>Luca Van Assche</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>Luca Van Assche</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:12.259620Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>7eedece37a8142f6</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181836</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.567487</v>
+      </c>
+      <c r="P6" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q6" s="28" t="n">
+        <v>0.077291</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="n"/>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n"/>
+      <c r="AD6" s="24" t="n"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Corentin Moutet p=0.433 vs Marton Fucsovics. Executable ask 0.4900 (aec-atp-marfuc-cormou-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:10.755068Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>16a5dd21c23e4790</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:51:36.214335Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>Alexis Galarneau</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.57909</v>
+      </c>
+      <c r="P7" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q7" s="28" t="n">
+        <v>0.088894</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n"/>
+      <c r="AD7" s="24" t="n"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Vit Kopriva p=0.579 vs Alexis Galarneau. Executable ask 0.4900 (aec-atp-alegal-vitkop-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>Alexis Galarneau</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>Alexis Galarneau</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>Alexis Galarneau</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:20.160476Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
